--- a/TIME TABLE SAMPLE DATA/INPUTS/faculty-availability-template.xlsx
+++ b/TIME TABLE SAMPLE DATA/INPUTS/faculty-availability-template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ganig\Desktop\Time_Table_\TIME TABLE SAMPLE DATA\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5afc8f5c19c83632/Desktop/Timetable/TIME TABLE SAMPLE DATA/INPUTS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F724CA75-D5DF-4AB4-8F73-4B34E9355C7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{F724CA75-D5DF-4AB4-8F73-4B34E9355C7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C99A8848-6912-4E85-8D65-23A81D4244A5}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>Faculty ID</t>
   </si>
@@ -59,6 +59,9 @@
   </si>
   <si>
     <t>5,6,7,1,2,3</t>
+  </si>
+  <si>
+    <t>6,7</t>
   </si>
 </sst>
 </file>
@@ -421,10 +424,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:G3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -447,7 +450,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>21</v>
       </c>
@@ -468,6 +471,14 @@
       </c>
       <c r="G2" t="s">
         <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>82</v>
+      </c>
+      <c r="F3" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
